--- a/artfynd/A 27029-2025 artfynd.xlsx
+++ b/artfynd/A 27029-2025 artfynd.xlsx
@@ -675,48 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125929757</v>
+        <v>125929579</v>
       </c>
       <c r="B2" t="n">
-        <v>79585</v>
+        <v>56843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488495</v>
+        <v>488368</v>
       </c>
       <c r="R2" t="n">
-        <v>6819695</v>
+        <v>6819719</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,65 +765,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125929579</v>
+        <v>125929757</v>
       </c>
       <c r="B3" t="n">
-        <v>56843</v>
+        <v>79585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488368</v>
+        <v>488495</v>
       </c>
       <c r="R3" t="n">
-        <v>6819719</v>
+        <v>6819695</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,62 +862,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125930232</v>
+        <v>125930245</v>
       </c>
       <c r="B4" t="n">
-        <v>56843</v>
+        <v>91247</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vassjöån, Vassjöån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488595</v>
+        <v>488593</v>
       </c>
       <c r="R4" t="n">
-        <v>6819763</v>
+        <v>6819760</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -976,45 +971,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125930245</v>
+        <v>125930232</v>
       </c>
       <c r="B5" t="n">
-        <v>91247</v>
+        <v>56843</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vassjöån, Vassjöån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488593</v>
+        <v>488595</v>
       </c>
       <c r="R5" t="n">
-        <v>6819760</v>
+        <v>6819763</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 27029-2025 artfynd.xlsx
+++ b/artfynd/A 27029-2025 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125929579</v>
+        <v>125929757</v>
       </c>
       <c r="B2" t="n">
-        <v>56843</v>
+        <v>79586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488368</v>
+        <v>488495</v>
       </c>
       <c r="R2" t="n">
-        <v>6819719</v>
+        <v>6819695</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,60 +760,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125929757</v>
+        <v>125929579</v>
       </c>
       <c r="B3" t="n">
-        <v>79585</v>
+        <v>56843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488495</v>
+        <v>488368</v>
       </c>
       <c r="R3" t="n">
-        <v>6819695</v>
+        <v>6819719</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,57 +862,62 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125930245</v>
+        <v>125930232</v>
       </c>
       <c r="B4" t="n">
-        <v>91247</v>
+        <v>56843</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vassjöån, Vassjöån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488593</v>
+        <v>488595</v>
       </c>
       <c r="R4" t="n">
-        <v>6819760</v>
+        <v>6819763</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -971,50 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125930232</v>
+        <v>125930245</v>
       </c>
       <c r="B5" t="n">
-        <v>56843</v>
+        <v>91248</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vassjöån, Vassjöån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488595</v>
+        <v>488593</v>
       </c>
       <c r="R5" t="n">
-        <v>6819763</v>
+        <v>6819760</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1076,7 +1076,7 @@
         <v>125930195</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>125929562</v>
       </c>
       <c r="B7" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>125929599</v>
       </c>
       <c r="B8" t="n">
-        <v>91247</v>
+        <v>91248</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>125929647</v>
       </c>
       <c r="B9" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27029-2025 artfynd.xlsx
+++ b/artfynd/A 27029-2025 artfynd.xlsx
@@ -874,50 +874,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125930232</v>
+        <v>125930245</v>
       </c>
       <c r="B4" t="n">
-        <v>56843</v>
+        <v>91248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vassjöån, Vassjöån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488595</v>
+        <v>488593</v>
       </c>
       <c r="R4" t="n">
-        <v>6819763</v>
+        <v>6819760</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -976,45 +971,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125930245</v>
+        <v>125930232</v>
       </c>
       <c r="B5" t="n">
-        <v>91248</v>
+        <v>56843</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vassjöån, Vassjöån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488593</v>
+        <v>488595</v>
       </c>
       <c r="R5" t="n">
-        <v>6819760</v>
+        <v>6819763</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 27029-2025 artfynd.xlsx
+++ b/artfynd/A 27029-2025 artfynd.xlsx
@@ -675,48 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125929757</v>
+        <v>125929579</v>
       </c>
       <c r="B2" t="n">
-        <v>79586</v>
+        <v>56843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488495</v>
+        <v>488368</v>
       </c>
       <c r="R2" t="n">
-        <v>6819695</v>
+        <v>6819719</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,65 +765,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125929579</v>
+        <v>125929757</v>
       </c>
       <c r="B3" t="n">
-        <v>56843</v>
+        <v>79590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488368</v>
+        <v>488495</v>
       </c>
       <c r="R3" t="n">
-        <v>6819719</v>
+        <v>6819695</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,12 +862,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -877,7 +877,7 @@
         <v>125930245</v>
       </c>
       <c r="B4" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125930195</v>
+        <v>125929562</v>
       </c>
       <c r="B6" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,17 +1104,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vassjöån, Vassjöån, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488594</v>
+        <v>488358</v>
       </c>
       <c r="R6" t="n">
-        <v>6819757</v>
+        <v>6819718</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125929562</v>
+        <v>125930195</v>
       </c>
       <c r="B7" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,17 +1201,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Vassjöån, Vassjöån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488358</v>
+        <v>488594</v>
       </c>
       <c r="R7" t="n">
-        <v>6819718</v>
+        <v>6819757</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>125929599</v>
       </c>
       <c r="B8" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>125929647</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27029-2025 artfynd.xlsx
+++ b/artfynd/A 27029-2025 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125929579</v>
+        <v>125929757</v>
       </c>
       <c r="B2" t="n">
-        <v>56843</v>
+        <v>79590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488368</v>
+        <v>488495</v>
       </c>
       <c r="R2" t="n">
-        <v>6819719</v>
+        <v>6819695</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,60 +760,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125929757</v>
+        <v>125929579</v>
       </c>
       <c r="B3" t="n">
-        <v>79590</v>
+        <v>56843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488495</v>
+        <v>488368</v>
       </c>
       <c r="R3" t="n">
-        <v>6819695</v>
+        <v>6819719</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,12 +862,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125929562</v>
+        <v>125930195</v>
       </c>
       <c r="B6" t="n">
         <v>78972</v>
@@ -1104,17 +1104,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Vassjöån, Vassjöån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488358</v>
+        <v>488594</v>
       </c>
       <c r="R6" t="n">
-        <v>6819718</v>
+        <v>6819757</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125930195</v>
+        <v>125929562</v>
       </c>
       <c r="B7" t="n">
         <v>78972</v>
@@ -1201,17 +1201,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vassjöån, Vassjöån, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488594</v>
+        <v>488358</v>
       </c>
       <c r="R7" t="n">
-        <v>6819757</v>
+        <v>6819718</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 27029-2025 artfynd.xlsx
+++ b/artfynd/A 27029-2025 artfynd.xlsx
@@ -874,45 +874,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125930245</v>
+        <v>125930232</v>
       </c>
       <c r="B4" t="n">
-        <v>91252</v>
+        <v>56843</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vassjöån, Vassjöån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488593</v>
+        <v>488595</v>
       </c>
       <c r="R4" t="n">
-        <v>6819760</v>
+        <v>6819763</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -971,50 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125930232</v>
+        <v>125930245</v>
       </c>
       <c r="B5" t="n">
-        <v>56843</v>
+        <v>91252</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vassjöån, Vassjöån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488595</v>
+        <v>488593</v>
       </c>
       <c r="R5" t="n">
-        <v>6819763</v>
+        <v>6819760</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 27029-2025 artfynd.xlsx
+++ b/artfynd/A 27029-2025 artfynd.xlsx
@@ -675,48 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125929757</v>
+        <v>125929579</v>
       </c>
       <c r="B2" t="n">
-        <v>79590</v>
+        <v>56844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488495</v>
+        <v>488368</v>
       </c>
       <c r="R2" t="n">
-        <v>6819695</v>
+        <v>6819719</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,65 +765,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125929579</v>
+        <v>125929757</v>
       </c>
       <c r="B3" t="n">
-        <v>56843</v>
+        <v>79591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488368</v>
+        <v>488495</v>
       </c>
       <c r="R3" t="n">
-        <v>6819719</v>
+        <v>6819695</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,12 +862,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -877,7 +877,7 @@
         <v>125930232</v>
       </c>
       <c r="B4" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>125930245</v>
       </c>
       <c r="B5" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>125930195</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>125929562</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>125929599</v>
       </c>
       <c r="B8" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>125929647</v>
       </c>
       <c r="B9" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27029-2025 artfynd.xlsx
+++ b/artfynd/A 27029-2025 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125929579</v>
+        <v>125929757</v>
       </c>
       <c r="B2" t="n">
-        <v>56844</v>
+        <v>79591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488368</v>
+        <v>488495</v>
       </c>
       <c r="R2" t="n">
-        <v>6819719</v>
+        <v>6819695</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,60 +760,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125929757</v>
+        <v>125929579</v>
       </c>
       <c r="B3" t="n">
-        <v>79591</v>
+        <v>56844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488495</v>
+        <v>488368</v>
       </c>
       <c r="R3" t="n">
-        <v>6819695</v>
+        <v>6819719</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,62 +862,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125930232</v>
+        <v>125930245</v>
       </c>
       <c r="B4" t="n">
-        <v>56844</v>
+        <v>91256</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vassjöån, Vassjöån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488595</v>
+        <v>488593</v>
       </c>
       <c r="R4" t="n">
-        <v>6819763</v>
+        <v>6819760</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -976,45 +971,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125930245</v>
+        <v>125930232</v>
       </c>
       <c r="B5" t="n">
-        <v>91254</v>
+        <v>56844</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vassjöån, Vassjöån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488593</v>
+        <v>488595</v>
       </c>
       <c r="R5" t="n">
-        <v>6819760</v>
+        <v>6819763</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1270,7 +1270,7 @@
         <v>125929599</v>
       </c>
       <c r="B8" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27029-2025 artfynd.xlsx
+++ b/artfynd/A 27029-2025 artfynd.xlsx
@@ -675,48 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125929757</v>
+        <v>125929579</v>
       </c>
       <c r="B2" t="n">
-        <v>79591</v>
+        <v>56844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488495</v>
+        <v>488368</v>
       </c>
       <c r="R2" t="n">
-        <v>6819695</v>
+        <v>6819719</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,65 +765,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125929579</v>
+        <v>125929757</v>
       </c>
       <c r="B3" t="n">
-        <v>56844</v>
+        <v>79591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488368</v>
+        <v>488495</v>
       </c>
       <c r="R3" t="n">
-        <v>6819719</v>
+        <v>6819695</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,12 +862,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -877,7 +877,7 @@
         <v>125930245</v>
       </c>
       <c r="B4" t="n">
-        <v>91256</v>
+        <v>91258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>125929599</v>
       </c>
       <c r="B8" t="n">
-        <v>91256</v>
+        <v>91258</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27029-2025 artfynd.xlsx
+++ b/artfynd/A 27029-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125929579</v>
       </c>
       <c r="B2" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125929757</v>
       </c>
       <c r="B3" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125930245</v>
       </c>
       <c r="B4" t="n">
-        <v>91258</v>
+        <v>91262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>125930232</v>
       </c>
       <c r="B5" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>125930195</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>125929562</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>125929599</v>
       </c>
       <c r="B8" t="n">
-        <v>91258</v>
+        <v>91262</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>125929647</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27029-2025 artfynd.xlsx
+++ b/artfynd/A 27029-2025 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125929579</v>
+        <v>125929757</v>
       </c>
       <c r="B2" t="n">
-        <v>56848</v>
+        <v>79595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488368</v>
+        <v>488495</v>
       </c>
       <c r="R2" t="n">
-        <v>6819719</v>
+        <v>6819695</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,60 +760,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125929757</v>
+        <v>125929579</v>
       </c>
       <c r="B3" t="n">
-        <v>79595</v>
+        <v>56848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488495</v>
+        <v>488368</v>
       </c>
       <c r="R3" t="n">
-        <v>6819695</v>
+        <v>6819719</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,12 +862,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 27029-2025 artfynd.xlsx
+++ b/artfynd/A 27029-2025 artfynd.xlsx
@@ -675,48 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125929757</v>
+        <v>125929579</v>
       </c>
       <c r="B2" t="n">
-        <v>79595</v>
+        <v>56848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488495</v>
+        <v>488368</v>
       </c>
       <c r="R2" t="n">
-        <v>6819695</v>
+        <v>6819719</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,65 +765,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125929579</v>
+        <v>125929757</v>
       </c>
       <c r="B3" t="n">
-        <v>56848</v>
+        <v>79595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488368</v>
+        <v>488495</v>
       </c>
       <c r="R3" t="n">
-        <v>6819719</v>
+        <v>6819695</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,12 +862,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 27029-2025 artfynd.xlsx
+++ b/artfynd/A 27029-2025 artfynd.xlsx
@@ -874,45 +874,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125930245</v>
+        <v>125930232</v>
       </c>
       <c r="B4" t="n">
-        <v>91262</v>
+        <v>56848</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vassjöån, Vassjöån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488593</v>
+        <v>488595</v>
       </c>
       <c r="R4" t="n">
-        <v>6819760</v>
+        <v>6819763</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -971,50 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125930232</v>
+        <v>125930245</v>
       </c>
       <c r="B5" t="n">
-        <v>56848</v>
+        <v>91262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vassjöån, Vassjöån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488595</v>
+        <v>488593</v>
       </c>
       <c r="R5" t="n">
-        <v>6819763</v>
+        <v>6819760</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 27029-2025 artfynd.xlsx
+++ b/artfynd/A 27029-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125929757</v>
       </c>
       <c r="B2" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125929579</v>
       </c>
       <c r="B3" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,50 +874,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125930232</v>
+        <v>125930245</v>
       </c>
       <c r="B4" t="n">
-        <v>56848</v>
+        <v>91265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vassjöån, Vassjöån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488595</v>
+        <v>488593</v>
       </c>
       <c r="R4" t="n">
-        <v>6819763</v>
+        <v>6819760</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -976,45 +971,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125930245</v>
+        <v>125930232</v>
       </c>
       <c r="B5" t="n">
-        <v>91262</v>
+        <v>56849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vassjöån, Vassjöån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488593</v>
+        <v>488595</v>
       </c>
       <c r="R5" t="n">
-        <v>6819760</v>
+        <v>6819763</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1076,7 +1076,7 @@
         <v>125930195</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>125929562</v>
       </c>
       <c r="B7" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>125929599</v>
       </c>
       <c r="B8" t="n">
-        <v>91262</v>
+        <v>91265</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>125929647</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27029-2025 artfynd.xlsx
+++ b/artfynd/A 27029-2025 artfynd.xlsx
@@ -675,48 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125929757</v>
+        <v>125929579</v>
       </c>
       <c r="B2" t="n">
-        <v>79598</v>
+        <v>56849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488495</v>
+        <v>488368</v>
       </c>
       <c r="R2" t="n">
-        <v>6819695</v>
+        <v>6819719</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,65 +765,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125929579</v>
+        <v>125929757</v>
       </c>
       <c r="B3" t="n">
-        <v>56849</v>
+        <v>79598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488368</v>
+        <v>488495</v>
       </c>
       <c r="R3" t="n">
-        <v>6819719</v>
+        <v>6819695</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,12 +862,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 27029-2025 artfynd.xlsx
+++ b/artfynd/A 27029-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125929579</v>
+        <v>125929599</v>
       </c>
       <c r="B2" t="n">
-        <v>56849</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488368</v>
+        <v>488416</v>
       </c>
       <c r="R2" t="n">
-        <v>6819719</v>
+        <v>6819684</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125929757</v>
+        <v>125930006</v>
       </c>
       <c r="B3" t="n">
-        <v>79598</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488495</v>
+        <v>488571</v>
       </c>
       <c r="R3" t="n">
-        <v>6819695</v>
+        <v>6819726</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -877,7 +872,7 @@
         <v>125930245</v>
       </c>
       <c r="B4" t="n">
-        <v>91265</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,53 +966,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125930232</v>
+        <v>125930496</v>
       </c>
       <c r="B5" t="n">
-        <v>56849</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vassjöån, Vassjöån, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488595</v>
+        <v>488509</v>
       </c>
       <c r="R5" t="n">
-        <v>6819763</v>
+        <v>6819704</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1047,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Remarkabel täthet av tallticka i området.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1061,26 +1056,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125930195</v>
+        <v>125929562</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1104,17 +1099,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vassjöån, Vassjöån, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488594</v>
+        <v>488358</v>
       </c>
       <c r="R6" t="n">
-        <v>6819757</v>
+        <v>6819718</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1170,14 +1165,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125929562</v>
+        <v>125929647</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1205,13 +1200,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488358</v>
+        <v>488466</v>
       </c>
       <c r="R7" t="n">
-        <v>6819718</v>
+        <v>6819684</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1267,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125929599</v>
+        <v>125929854</v>
       </c>
       <c r="B8" t="n">
-        <v>91265</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,13 +1297,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488416</v>
+        <v>488530</v>
       </c>
       <c r="R8" t="n">
-        <v>6819684</v>
+        <v>6819699</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1352,26 +1347,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125929647</v>
+        <v>125929878</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1399,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488466</v>
+        <v>488531</v>
       </c>
       <c r="R9" t="n">
-        <v>6819684</v>
+        <v>6819719</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1458,6 +1453,1088 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125930084</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Heros, Heros, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>488556</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6819742</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125930120</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vassjöån, Vassjöån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>488569</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6819748</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125930195</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vassjöån, Vassjöån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>488594</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6819757</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125929841</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Heros, Heros, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>488514</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6819708</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125929757</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Heros, Heros, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>488495</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6819695</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125929898</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Heros, Heros, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>488535</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6819734</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125929579</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Heros, Heros, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>488368</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6819719</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125930232</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vassjöån, Vassjöån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>488595</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6819763</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125930331</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Heros, Heros, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>488560</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6819730</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125929760</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Heros, Heros, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>488510</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6819704</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125929848</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Heros, Heros, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>488514</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6819708</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27029-2025 artfynd.xlsx
+++ b/artfynd/A 27029-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125929599</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125930006</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125930245</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125930496</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125929562</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125929647</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125929854</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125929878</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125930084</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125930120</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125930195</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125929841</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1938,6 +2003,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125929757</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2035,6 +2105,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125929898</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2137,6 +2212,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125929579</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2239,6 +2319,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125930232</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2341,6 +2426,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125930331</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2438,6 +2528,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125929760</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2535,8 +2630,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125929848</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>